--- a/stories/arbres/ATOM-SEC.RUE.003-06.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.003-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Constantin sort avec maman. Ils marchent dans la rue. Constantin reste près de l'adulte. Il prend la main de maman. Il tient aussi le manteau. Main ou manteau. Ses pieds marchent à côté. Maman dit : près de moi. Constantin sent le manteau. Le manteau est doux. La main de maman est chaude. Constantin marche à côté. Ils passent le marché. Constantin sent les oranges. Il reste près de l'adulte. La main tient le manteau. Maman sourit. Constantin sourit aussi. Ils rentrent ensemble. Constantin garde la main. Il reste près de l'adulte.</t>
+          <t>Constantin sort avec maman. Ils marchent dans la rue. Constantin reste près de l'adulte. Il prend la main de maman. Il tient aussi le manteau. Main ou manteau. Ses pieds marchent à côté. Près de moi. Constantin sent le manteau. Le manteau est doux. La main de maman est chaude. Constantin marche à côté. Ils passent le marché. Constantin sent les oranges. Il reste près de l'adulte. La main tient le manteau. Maman sourit. Constantin sourit aussi. Ils rentrent ensemble. Constantin garde la main. Il reste près de l'adulte.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,13 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Constantin sort avec maman. Ils marchent dans la rue. Constantin reste près de l'adulte. Il prend la main de maman. Il tient aussi le manteau. Main ou manteau. Ses pieds marchent à côté.
+maman|Près de moi.
+narrateur|Constantin sent le manteau. Le manteau est doux. La main de maman est chaude. Constantin marche à côté. Ils passent le marché. Constantin sent les oranges. Il reste près de l'adulte. La main tient le manteau. Maman sourit. Constantin sourit aussi. Ils rentrent ensemble. Constantin garde la main. Il reste près de l'adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Constantin marche dans la rue. Où est-il ?</t>
         </is>
       </c>
     </row>
@@ -1641,6 +1669,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Constantin est près de maman. La main tient le manteau. Maman est là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1807,6 +1840,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Constantin garde la main de maman. Ils rentrent à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1969,6 +2007,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1987,7 +2030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2004,6 +2047,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.RUE.003-06.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.003-06.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1312,6 +1317,7 @@
 narrateur|Constantin sent le manteau. Le manteau est doux. La main de maman est chaude. Constantin marche à côté. Ils passent le marché. Constantin sent les oranges. Il reste près de l'adulte. La main tient le manteau. Maman sourit. Constantin sourit aussi. Ils rentrent ensemble. Constantin garde la main. Il reste près de l'adulte.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1505,7 @@
           <t>narrateur|Constantin marche dans la rue. Où est-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1674,6 +1681,7 @@
           <t>narrateur|Constantin est près de maman. La main tient le manteau. Maman est là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1845,6 +1853,7 @@
           <t>narrateur|Constantin garde la main de maman. Ils rentrent à la maison.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2012,6 +2021,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2030,7 +2040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2054,6 +2064,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2068,7 +2092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2255,6 +2279,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SEC.RUE.003-06.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.003-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Constantin près de maman</t>
+          <t>La sente et la fleur</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Nino veut une fleur bleue pour la table, puis le pain du village. Un caillou roule sur la sente. Il reste près de maman. La sente rejoint la rue. Puis la fleur et le pain.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Constantin sort avec maman. Ils marchent dans la rue. Constantin reste près de l'adulte. Il prend la main de maman. Il tient aussi le manteau. Main ou manteau. Ses pieds marchent à côté. Près de moi. Constantin sent le manteau. Le manteau est doux. La main de maman est chaude. Constantin marche à côté. Ils passent le marché. Constantin sent les oranges. Il reste près de l'adulte. La main tient le manteau. Maman sourit. Constantin sourit aussi. Ils rentrent ensemble. Constantin garde la main. Il reste près de l'adulte.</t>
+          <t>Un caillou chaud roule dans l'herbe sèche. La sente sent le thym et la poussière. Une fleur bleue penche au bord du chemin. Loin, une clochette de chèvre tinte. Le vent porte un peu de résine. Nino vit ici, avec maman. Maman, la fleur est bleue ! Oui. Elle sent un peu le miel. Tu as entendu la clochette ? La chèvre est là-haut. En ce moment, Nino prend le manteau. Le manteau de maman sent le thym. Je veux la fleur pour la table ! On y va. Tu restes près de moi. Ils marchent sur la sente étroite. L'herbe sèche racle les chaussures. Le caillou chaud redescend un peu. Il roule ! On le laisse. Toi, tu restes près. Nino se serre contre maman. Il garde le manteau. Bravo. Maman cueille la fleur, tout près. Nino la voit, sans lâcher le tissu. Elle est douce. Oui. Maintenant, la rue. La sente rejoint les premières maisons. La rue sent déjà le pain. Le village ! On reste près aussi. Tu tiens le manteau ? Oui. Nino marche à côté, sur le trottoir. La fleur bleue tremble dans la main de maman. Tu marches à côté ? À côté. Leurs ombres se collent au mur. La clochette tinte plus loin. Je veux le pain aussi. Merci d'être resté près. Nino serre encore le manteau. Le thym de la sente reste dans l'air.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Constantin sort avec maman. Ils marchent dans la rue. Constantin reste &lt;emphasis level="moderate"&gt;près&lt;/emphasis&gt; de l'adulte. Il prend la main de maman. Il tient aussi le manteau. Main ou manteau. Ses pieds marchent à côté. Maman dit : près de moi. Constantin sent le manteau. Le manteau est doux. La main de maman est chaude. Constantin marche à côté. Ils passent le marché. Constantin sent les oranges. Il reste près de l'adulte. La main tient le manteau. Maman sourit. Constantin sourit aussi. Ils rentrent ensemble. Constantin garde la main. Il reste près de l'adulte.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un caillou chaud roule dans l'herbe sèche. La sente sent le thym et la poussière. Une fleur bleue penche au bord du chemin. Loin, une clochette de chèvre tinte. Le vent porte un peu de résine. Nino vit ici, avec maman. Maman, la fleur est bleue ! Oui. Elle sent un peu le miel. Tu as entendu la clochette ? La chèvre est là-haut. En ce moment, Nino prend le manteau. Le manteau de maman sent le thym. Je veux la fleur pour la table ! On y va. Tu restes près de moi. Ils marchent sur la sente étroite. L'herbe sèche racle les chaussures. Le caillou chaud redescend un peu. Il roule ! On le laisse. Toi, tu restes près. Nino se serre contre maman. Il garde le manteau. Bravo. Maman cueille la fleur, tout près. Nino la voit, sans lâcher le tissu. Elle est douce. Oui. Maintenant, la rue. La sente rejoint les premières maisons. La rue sent déjà le pain. Le village ! On reste près aussi. Tu tiens le manteau ? Oui. Nino marche à côté, sur le trottoir. La fleur bleue tremble dans la main de maman. Tu marches à côté ? À côté. Leurs ombres se collent au mur. La clochette tinte plus loin. Je veux le pain aussi. Merci d'être resté près. Nino serre encore le manteau. Le thym de la sente reste dans l'air.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1233,14 +1245,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA2" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,12 +1324,59 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Constantin sort avec maman. Ils marchent dans la rue. Constantin reste près de l'adulte. Il prend la main de maman. Il tient aussi le manteau. Main ou manteau. Ses pieds marchent à côté.
-maman|Près de moi.
-narrateur|Constantin sent le manteau. Le manteau est doux. La main de maman est chaude. Constantin marche à côté. Ils passent le marché. Constantin sent les oranges. Il reste près de l'adulte. La main tient le manteau. Maman sourit. Constantin sourit aussi. Ils rentrent ensemble. Constantin garde la main. Il reste près de l'adulte.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Un caillou chaud roule dans l'herbe sèche.
+narrateur|La sente sent le thym et la poussière.
+narrateur|Une fleur bleue penche au bord du chemin.
+narrateur|Loin, une clochette de chèvre tinte.
+narrateur|Le vent porte un peu de résine.
+narrateur|Nino vit ici, avec maman.
+enfant-m|Maman, la fleur est bleue !
+maman|Oui.
+maman|Elle sent un peu le miel.
+maman|Tu as entendu la clochette ?
+enfant-m|La chèvre est là-haut.
+narrateur|En ce moment, Nino prend le manteau.
+narrateur|Le manteau de maman sent le thym.
+enfant-m|Je veux la fleur pour la table !
+maman|On y va.
+maman|Tu restes près de moi.
+narrateur|Ils marchent sur la sente étroite.
+narrateur|L'herbe sèche racle les chaussures.
+narrateur|Le caillou chaud redescend un peu.
+enfant-m|Il roule !
+maman|On le laisse.
+maman|Toi, tu restes près.
+narrateur|Nino se serre contre maman.
+narrateur|Il garde le manteau.
+maman|Bravo.
+narrateur|Maman cueille la fleur, tout près.
+narrateur|Nino la voit, sans lâcher le tissu.
+enfant-m|Elle est douce.
+maman|Oui.
+maman|Maintenant, la rue.
+narrateur|La sente rejoint les premières maisons.
+narrateur|La rue sent déjà le pain.
+enfant-m|Le village !
+maman|On reste près aussi.
+maman|Tu tiens le manteau ?
+enfant-m|Oui.
+narrateur|Nino marche à côté, sur le trottoir.
+narrateur|La fleur bleue tremble dans la main de maman.
+maman|Tu marches à côté ?
+enfant-m|À côté.
+narrateur|Leurs ombres se collent au mur.
+narrateur|La clochette tinte plus loin.
+enfant-m|Je veux le pain aussi.
+maman|Merci d'être resté près.
+narrateur|Nino serre encore le manteau.
+narrateur|Le thym de la sente reste dans l'air.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>oiseau</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1342,12 +1401,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Constantin marche dans la rue. Où est-il ?</t>
+          <t>Nino marche sur la sente. Où est-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Constantin marche dans la rue. Où est-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino marche sur la sente. Où est-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1362,7 +1421,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>près de maman | près | la main | manteau | à côté</t>
+          <t>près | près de maman | à côté | la main | le manteau | sur la sente</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1377,7 +1436,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Il reste près. Il tient la main. Où est Constantin ?</t>
+          <t>Il reste près de maman. Où est Nino ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1426,7 +1485,7 @@
         <v>0.8</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1502,10 +1561,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Constantin marche dans la rue. Où est-il ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Nino marche sur la sente.
+narrateur|Où est-il ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1530,12 +1589,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Constantin est près de maman. La main tient le manteau. Maman est là.</t>
+          <t>Nino est près de maman. La main tient le manteau. Sur la sente, puis dans la rue. Tu es resté près de moi ? Oui. J'ai tenu le manteau. Bravo, Nino. Près de moi. Le manteau sent encore le thym. La fleur bleue tremble un peu. Le pain du village sent plus fort.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Constantin est &lt;emphasis level="moderate"&gt;près&lt;/emphasis&gt; de maman. La main tient le manteau. Maman est là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino est près de maman. La main tient le manteau. Sur la sente, puis dans la rue. Tu es resté près de moi ? Oui. J'ai tenu le manteau. Bravo, Nino. Près de moi. Le manteau sent encore le thym. La fleur bleue tremble un peu. Le pain du village sent plus fort.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1591,14 +1650,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA4" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1678,10 +1737,19 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Constantin est près de maman. La main tient le manteau. Maman est là.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Nino est près de maman.
+narrateur|La main tient le manteau.
+narrateur|Sur la sente, puis dans la rue.
+maman|Tu es resté près de moi ?
+enfant-m|Oui.
+enfant-m|J'ai tenu le manteau.
+maman|Bravo, Nino.
+maman|Près de moi.
+narrateur|Le manteau sent encore le thym.
+narrateur|La fleur bleue tremble un peu.
+narrateur|Le pain du village sent plus fort.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1706,12 +1774,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Constantin garde la main de maman. Ils rentrent à la maison.</t>
+          <t>La boulangerie ouvre sa porte. Tu prends le pain ? Nino tient le pain, et le manteau. Il est chaud ! Oui. Tu es resté près. La fleur bleue voyage à côté. Ça sent le miel et le four. Pour la table. Oui. Ils rentrent par la rue, tout près. Puis la sente remonte un peu. La chèvre tinte encore. Oui. On rentre près l'un de l'autre. L'herbe sèche racle encore. Le pain chauffe les mains de Nino.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Constantin garde la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt; de maman. Ils rentrent à la maison.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>La boulangerie ouvre sa porte. Tu prends le pain ? Nino tient le pain, et le manteau. Il est chaud ! Oui. Tu es resté près. La fleur bleue voyage à côté. Ça sent le miel et le four. Pour la table. Oui. Ils rentrent par la rue, tout près. Puis la sente remonte un peu. La chèvre tinte encore. Oui. On rentre près l'un de l'autre. L'herbe sèche racle encore. Le pain chauffe les mains de Nino.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1767,14 +1835,14 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA5" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1850,10 +1918,25 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Constantin garde la main de maman. Ils rentrent à la maison.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|La boulangerie ouvre sa porte.
+maman|Tu prends le pain ?
+narrateur|Nino tient le pain, et le manteau.
+enfant-m|Il est chaud !
+maman|Oui.
+maman|Tu es resté près.
+narrateur|La fleur bleue voyage à côté.
+narrateur|Ça sent le miel et le four.
+enfant-m|Pour la table.
+maman|Oui.
+narrateur|Ils rentrent par la rue, tout près.
+narrateur|Puis la sente remonte un peu.
+enfant-m|La chèvre tinte encore.
+maman|Oui.
+maman|On rentre près l'un de l'autre.
+narrateur|L'herbe sèche racle encore.
+narrateur|Le pain chauffe les mains de Nino.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1878,12 +1961,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>La fleur sent le miel. Oui. Merci d'être resté près. Le pain repose près de la fleur bleue. La clochette de la chèvre tinte tout loin.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>La fleur sent le miel. Oui. Merci d'être resté près. Le pain repose près de la fleur bleue. La clochette de la chèvre tinte tout loin.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1939,14 +2022,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.82</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2018,10 +2101,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>enfant-m|La fleur sent le miel.
+maman|Oui.
+maman|Merci d'être resté près.
+narrateur|Le pain repose près de la fleur bleue.
+narrateur|La clochette de la chèvre tinte tout loin.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2040,7 +2126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2078,6 +2164,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.RUE.003-06.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.003-06.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>rue vers le marché</t>
+          <t>sente de montagne qui rejoint la rue du village</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Constantin, maman</t>
+          <t>Nino, maman</t>
         </is>
       </c>
     </row>
